--- a/data/trans_orig/P6901-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6901-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87795</t>
+          <t>87337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101937</t>
+          <t>102176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>26737</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35580</t>
+          <t>35650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117492</t>
+          <t>117413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135364</t>
+          <t>135030</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>23949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>13824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31362</t>
+          <t>31441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203288</t>
+          <t>204623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233037</t>
+          <t>233377</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89492</t>
+          <t>88757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105719</t>
+          <t>105441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300378</t>
+          <t>299417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334149</t>
+          <t>334411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53908</t>
+          <t>53568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83657</t>
+          <t>82322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71366</t>
+          <t>71104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105137</t>
+          <t>106098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47819</t>
+          <t>48813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>33932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48254</t>
+          <t>48610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68468</t>
+          <t>68991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92351</t>
+          <t>92872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43108</t>
+          <t>44235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30746</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45707</t>
+          <t>45186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69590</t>
+          <t>69067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>334550</t>
+          <t>335509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>372165</t>
+          <t>372213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158216</t>
+          <t>158264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182869</t>
+          <t>183829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>501482</t>
+          <t>501537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>549421</t>
+          <t>546815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100140</t>
+          <t>100092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137755</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>36292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143006</t>
+          <t>145612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190945</t>
+          <t>190890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34620</t>
+          <t>34414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48866</t>
+          <t>48733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21467</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31957</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>61044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78350</t>
+          <t>78969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36442</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152345</t>
+          <t>155355</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180427</t>
+          <t>181617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100559</t>
+          <t>101392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118913</t>
+          <t>118696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263045</t>
+          <t>263923</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295028</t>
+          <t>294784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>40122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69394</t>
+          <t>66384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29138</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57241</t>
+          <t>57485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89224</t>
+          <t>88346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37775</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>33719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>68027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,52%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>23258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41620</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>225061</t>
+          <t>227148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258703</t>
+          <t>259487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153383</t>
+          <t>153048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178952</t>
+          <t>177544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387473</t>
+          <t>388684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>427464</t>
+          <t>429310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67892</t>
+          <t>67108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101534</t>
+          <t>99447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60278</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112791</t>
+          <t>110945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152782</t>
+          <t>151571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35294</t>
+          <t>34830</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49051</t>
+          <t>48774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>12158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>50914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65876</t>
+          <t>65665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>22691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>165270</t>
+          <t>164152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>190977</t>
+          <t>190198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105320</t>
+          <t>104027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118473</t>
+          <t>118191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277036</t>
+          <t>274368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305622</t>
+          <t>304810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>39184</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64112</t>
+          <t>65230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48325</t>
+          <t>49137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76911</t>
+          <t>79579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28981</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45891</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46659</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61732</t>
+          <t>62002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80289</t>
+          <t>80315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101811</t>
+          <t>103615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17637</t>
+          <t>17939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>27229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56947</t>
+          <t>56921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>241547</t>
+          <t>239483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275825</t>
+          <t>276137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171011</t>
+          <t>172284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192299</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>422253</t>
+          <t>421275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>461718</t>
+          <t>462913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72666</t>
+          <t>72354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106944</t>
+          <t>109008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45287</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103070</t>
+          <t>101875</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142535</t>
+          <t>143513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>28057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24540</t>
+          <t>24569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50519</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175089</t>
+          <t>172889</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>201190</t>
+          <t>200276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>189760</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216576</t>
+          <t>215422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>368779</t>
+          <t>370401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408398</t>
+          <t>408347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>39304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>66691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>22946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49199</t>
+          <t>48608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69550</t>
+          <t>69601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109169</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23878</t>
+          <t>23452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42460</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46278</t>
+          <t>46681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64067</t>
+          <t>64094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76393</t>
+          <t>75580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100426</t>
+          <t>101526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45648</t>
+          <t>46074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44417</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59795</t>
+          <t>58695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83828</t>
+          <t>84641</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>226773</t>
+          <t>227499</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262490</t>
+          <t>262476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>255263</t>
+          <t>254685</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297339</t>
+          <t>298217</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495487</t>
+          <t>496609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>551541</t>
+          <t>555133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,18%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75830</t>
+          <t>75844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111547</t>
+          <t>110821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56710</t>
+          <t>55832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98786</t>
+          <t>99364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140828</t>
+          <t>137236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196882</t>
+          <t>195760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
